--- a/2018/Beirut2/Beirut2_members_final.xlsx
+++ b/2018/Beirut2/Beirut2_members_final.xlsx
@@ -645,7 +645,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>حركة شباب لبنان</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -1725,7 +1725,7 @@
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
